--- a/data/trans_orig/LAWTONBRODY-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY-Habitat-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,15</t>
+          <t>6,33; 7,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,31</t>
+          <t>6,56; 7,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,3</t>
+          <t>6,55; 7,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,17</t>
+          <t>6,44; 7,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 6,71</t>
+          <t>5,88; 6,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 6,93</t>
+          <t>6,2; 6,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,1</t>
+          <t>6,51; 7,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 6,9</t>
+          <t>6,33; 6,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 6,99</t>
+          <t>6,48; 7,03</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,26</t>
+          <t>6,63; 7,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 6,92</t>
+          <t>6,02; 6,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,31</t>
+          <t>6,72; 7,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,01</t>
+          <t>6,31; 6,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 6,22</t>
+          <t>5,37; 6,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,98</t>
+          <t>6,25; 6,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,04</t>
+          <t>6,56; 7,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 6,42</t>
+          <t>5,79; 6,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,05</t>
+          <t>6,57; 7,06</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,62</t>
+          <t>6,99; 7,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,07</t>
+          <t>5,88; 7,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 7,21</t>
+          <t>6,5; 7,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,52</t>
+          <t>5,45; 6,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,77</t>
+          <t>5,84; 6,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,33</t>
+          <t>6,83; 7,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 6,65</t>
+          <t>5,81; 6,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,05</t>
+          <t>6,41; 7,07</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,51</t>
+          <t>6,99; 7,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 7,19</t>
+          <t>6,42; 7,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,52</t>
+          <t>6,98; 7,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,0</t>
+          <t>6,38; 6,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 6,93</t>
+          <t>6,29; 6,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 6,98</t>
+          <t>6,33; 7,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 7,12</t>
+          <t>6,69; 7,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,94</t>
+          <t>6,41; 6,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,14</t>
+          <t>6,7; 7,16</t>
         </is>
       </c>
     </row>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 6,96</t>
+          <t>6,5; 6,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,28</t>
+          <t>6,99; 7,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 6,93</t>
+          <t>6,58; 6,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 6,43</t>
+          <t>6,01; 6,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,02</t>
+          <t>6,78; 7,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 6,59</t>
+          <t>6,3; 6,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 6,96</t>
+          <t>6,7; 6,95</t>
         </is>
       </c>
     </row>
